--- a/data/trans_camb/P29A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P29A_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 11,89</t>
+          <t>-1,54; 11,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 13,37</t>
+          <t>-0,12; 13,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 3,21</t>
+          <t>-9,38; 3,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 11,56</t>
+          <t>-5,36; 11,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 11,97</t>
+          <t>-4,49; 11,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 3,48</t>
+          <t>-10,16; 3,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 8,93</t>
+          <t>-2,13; 8,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 9,87</t>
+          <t>-0,77; 10,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 0,29</t>
+          <t>-9,39; 0,0</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 21,05</t>
+          <t>-2,28; 21,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 23,46</t>
+          <t>-0,01; 23,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 5,99</t>
+          <t>-15,18; 5,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 32,87</t>
+          <t>-12,61; 32,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 34,23</t>
+          <t>-10,08; 32,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 9,7</t>
+          <t>-22,98; 11,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 18,24</t>
+          <t>-3,92; 17,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 20,29</t>
+          <t>-1,36; 20,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 0,53</t>
+          <t>-17,28; -0,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 5,74</t>
+          <t>-8,51; 6,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 10,53</t>
+          <t>-4,86; 9,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,57; -5,06</t>
+          <t>-19,1; -4,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 6,55</t>
+          <t>-8,85; 6,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 18,01</t>
+          <t>3,38; 18,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 4,07</t>
+          <t>-9,58; 3,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 5,7</t>
+          <t>-5,16; 5,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 12,05</t>
+          <t>2,35; 12,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,78; -1,57</t>
+          <t>-11,95; -1,99</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 10,36</t>
+          <t>-13,73; 12,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 18,83</t>
+          <t>-7,71; 18,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,08; -9,47</t>
+          <t>-30,31; -8,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 19,21</t>
+          <t>-21,38; 19,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 51,77</t>
+          <t>8,22; 54,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 12,43</t>
+          <t>-22,29; 9,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 12,43</t>
+          <t>-10,2; 12,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 26,34</t>
+          <t>4,47; 27,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,11; -3,46</t>
+          <t>-23,44; -4,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 3,73</t>
+          <t>-8,46; 3,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 8,26</t>
+          <t>-3,86; 8,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-49,48; -8,91</t>
+          <t>-47,89; -7,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 0,92</t>
+          <t>-16,99; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 8,59</t>
+          <t>-14,32; 8,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -1,32</t>
+          <t>-17,91; 0,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,18; -0,52</t>
+          <t>-11,25; -0,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 6,42</t>
+          <t>-4,44; 6,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-42,85; -9,42</t>
+          <t>-40,56; -9,37</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 6,64</t>
+          <t>-13,41; 6,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 14,55</t>
+          <t>-5,91; 14,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,49; -15,27</t>
+          <t>-79,61; -13,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,35; 2,91</t>
+          <t>-43,21; 3,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 31,65</t>
+          <t>-35,55; 27,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,45; -4,33</t>
+          <t>-46,78; 0,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -0,88</t>
+          <t>-20,05; -0,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 12,82</t>
+          <t>-7,64; 13,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,98; -17,57</t>
+          <t>-71,76; -17,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 5,77</t>
+          <t>-2,31; 5,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,64</t>
+          <t>-0,02; 8,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 2,76</t>
+          <t>-6,1; 2,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 4,93</t>
+          <t>-4,58; 4,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,95</t>
+          <t>3,56; 12,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 44,15</t>
+          <t>0,17; 45,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,45</t>
+          <t>-2,9; 3,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,9</t>
+          <t>1,19; 7,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 19,29</t>
+          <t>-2,88; 21,86</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 11,89</t>
+          <t>-4,59; 11,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 15,59</t>
+          <t>-0,13; 16,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 5,55</t>
+          <t>-11,58; 4,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 21,12</t>
+          <t>-16,17; 19,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,23; 55,55</t>
+          <t>12,92; 55,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 191,69</t>
+          <t>0,39; 183,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 8,5</t>
+          <t>-6,77; 8,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,36; 19,82</t>
+          <t>2,78; 19,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 47,55</t>
+          <t>-6,85; 58,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 5,11</t>
+          <t>-7,93; 6,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -3,39</t>
+          <t>-16,16; -2,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -1,94</t>
+          <t>-16,7; -2,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 2,66</t>
+          <t>-6,4; 3,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 5,75</t>
+          <t>-3,73; 5,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -2,4</t>
+          <t>-12,76; -3,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,94</t>
+          <t>-5,5; 2,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,72</t>
+          <t>-5,42; 3,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,11; -4,01</t>
+          <t>-14,87; -4,32</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 9,4</t>
+          <t>-12,92; 10,9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,76; -6,43</t>
+          <t>-25,87; -4,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,41; -3,84</t>
+          <t>-27,43; -4,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 13,01</t>
+          <t>-25,64; 14,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 28,64</t>
+          <t>-15,15; 28,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,41; -12,34</t>
+          <t>-50,48; -14,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 8,72</t>
+          <t>-14,23; 8,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 8,33</t>
+          <t>-13,98; 10,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-37,12; -11,96</t>
+          <t>-39,78; -13,02</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 13,37</t>
+          <t>-4,01; 12,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,35; 17,23</t>
+          <t>0,09; 16,25</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 7,19</t>
+          <t>-17,5; 7,2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,36</t>
+          <t>1,85; 8,44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,96</t>
+          <t>3,6; 10,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,6</t>
+          <t>-3,14; 3,55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,41</t>
+          <t>1,9; 7,9</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,91</t>
+          <t>4,12; 10,64</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 4,27</t>
+          <t>-3,51; 4,54</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 32,82</t>
+          <t>-7,71; 31,18</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,72; 42,66</t>
+          <t>0,1; 39,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-36,38; 16,5</t>
+          <t>-37,39; 16,53</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10,38; 56,8</t>
+          <t>11,21; 59,27</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>21,98; 70,13</t>
+          <t>21,19; 70,33</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 24,06</t>
+          <t>-18,74; 23,58</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,59; 41,95</t>
+          <t>8,33; 39,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>17,93; 55,02</t>
+          <t>18,35; 52,8</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 21,18</t>
+          <t>-15,95; 22,37</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,73</t>
+          <t>-1,1; 3,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,57</t>
+          <t>-0,08; 4,75</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-18,18; -4,51</t>
+          <t>-20,58; -4,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,3</t>
+          <t>-1,04; 3,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,39</t>
+          <t>4,07; 8,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 18,64</t>
+          <t>-1,48; 18,54</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,73</t>
+          <t>-0,53; 2,87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,83</t>
+          <t>2,31; 5,88</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 3,21</t>
+          <t>-6,44; 2,81</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 6,96</t>
+          <t>-1,96; 6,93</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 8,47</t>
+          <t>-0,11; 8,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-33,34; -8,28</t>
+          <t>-37,59; -8,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 13,93</t>
+          <t>-4,02; 14,09</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,57; 36,19</t>
+          <t>15,76; 35,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 78,3</t>
+          <t>-5,99; 76,47</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 6,96</t>
+          <t>-1,3; 7,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>6,06; 15,05</t>
+          <t>5,62; 15,27</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 8,29</t>
+          <t>-16,02; 7,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P29A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P29A_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>-3,84</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,97</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,44</t>
+          <t>-5,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 11,75</t>
+          <t>-2,17; 11,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 13,02</t>
+          <t>0,11; 13,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 3,01</t>
+          <t>-10,26; 3,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 11,62</t>
+          <t>-4,51; 11,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 11,1</t>
+          <t>-4,03; 11,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 3,76</t>
+          <t>-10,59; 2,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 8,67</t>
+          <t>-1,6; 8,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 10,05</t>
+          <t>-0,19; 9,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 0,0</t>
+          <t>-9,58; -0,12</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-5,09%</t>
+          <t>-6,49%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-7,55%</t>
+          <t>-8,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-8,65%</t>
+          <t>-9,93%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 21,15</t>
+          <t>-3,45; 20,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 23,35</t>
+          <t>0,07; 23,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 5,29</t>
+          <t>-16,26; 6,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 32,75</t>
+          <t>-10,37; 32,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 32,42</t>
+          <t>-9,67; 33,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 11,24</t>
+          <t>-24,15; 7,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 17,65</t>
+          <t>-3,11; 18,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 20,87</t>
+          <t>-0,46; 20,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,28; -0,03</t>
+          <t>-17,69; -0,27</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-12,2</t>
+          <t>-12,8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,88</t>
+          <t>-3,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,99</t>
+          <t>-7,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 6,81</t>
+          <t>-8,86; 6,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 9,98</t>
+          <t>-4,26; 11,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,1; -4,93</t>
+          <t>-19,43; -5,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 6,61</t>
+          <t>-7,94; 6,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 18,8</t>
+          <t>3,85; 18,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 3,3</t>
+          <t>-9,57; 3,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 5,82</t>
+          <t>-5,06; 5,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 12,75</t>
+          <t>1,38; 12,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,95; -1,99</t>
+          <t>-11,95; -1,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-20,58%</t>
+          <t>-21,58%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,58%</t>
+          <t>-9,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-14,37%</t>
+          <t>-15,79%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 12,44</t>
+          <t>-14,11; 12,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 18,4</t>
+          <t>-6,58; 20,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,31; -8,89</t>
+          <t>-31,58; -9,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 19,44</t>
+          <t>-19,15; 18,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 54,85</t>
+          <t>9,08; 54,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 9,82</t>
+          <t>-22,67; 8,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 12,37</t>
+          <t>-10,08; 12,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 27,8</t>
+          <t>2,57; 26,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,44; -4,36</t>
+          <t>-23,41; -4,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-28,44</t>
+          <t>-11,7</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,36</t>
+          <t>-8,67</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-23,59</t>
+          <t>-12,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 3,89</t>
+          <t>-8,9; 3,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 8,16</t>
+          <t>-3,74; 8,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-47,89; -7,76</t>
+          <t>-18,71; -5,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 0,88</t>
+          <t>-16,88; 1,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 8,37</t>
+          <t>-13,39; 8,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 0,05</t>
+          <t>-18,46; -0,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,25; -0,27</t>
+          <t>-10,65; -0,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 6,49</t>
+          <t>-4,39; 6,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-40,56; -9,37</t>
+          <t>-17,28; -6,8</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-47,39%</t>
+          <t>-19,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,83%</t>
+          <t>-25,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-43,92%</t>
+          <t>-22,36%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 6,81</t>
+          <t>-14,31; 6,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 14,21</t>
+          <t>-5,8; 14,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,61; -13,54</t>
+          <t>-29,9; -9,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 3,23</t>
+          <t>-43,6; 3,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 27,98</t>
+          <t>-34,08; 28,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 0,39</t>
+          <t>-46,54; 0,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,05; -0,64</t>
+          <t>-19,24; -0,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 13,01</t>
+          <t>-7,9; 11,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,76; -17,63</t>
+          <t>-30,87; -13,41</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-2,88</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,73</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>-2,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 5,74</t>
+          <t>-2,67; 6,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 8,11</t>
+          <t>-0,14; 8,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 2,5</t>
+          <t>-7,02; 1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 4,51</t>
+          <t>-4,42; 4,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,56; 12,93</t>
+          <t>3,72; 12,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 45,02</t>
+          <t>-3,51; 5,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,29</t>
+          <t>-2,92; 3,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,77</t>
+          <t>1,14; 7,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 21,86</t>
+          <t>-6,33; 0,11</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-3,24%</t>
+          <t>-5,64%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>-6,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 11,56</t>
+          <t>-4,92; 12,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 16,36</t>
+          <t>-0,34; 16,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 4,94</t>
+          <t>-13,42; 2,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 19,43</t>
+          <t>-15,92; 20,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,92; 55,85</t>
+          <t>13,61; 55,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 183,15</t>
+          <t>-12,45; 22,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 8,13</t>
+          <t>-6,81; 8,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 19,26</t>
+          <t>2,62; 19,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 58,21</t>
+          <t>-14,59; 0,3</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-9,5</t>
+          <t>-12,96</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-7,03</t>
+          <t>-4,19</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-8,65</t>
+          <t>-6,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 6,06</t>
+          <t>-8,52; 5,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -2,31</t>
+          <t>-16,51; -2,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,7; -2,42</t>
+          <t>-20,03; -5,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 3,0</t>
+          <t>-6,58; 2,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 5,9</t>
+          <t>-3,36; 6,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,76; -3,01</t>
+          <t>-8,91; 0,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 2,86</t>
+          <t>-5,69; 2,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 3,43</t>
+          <t>-5,81; 2,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,87; -4,32</t>
+          <t>-11,4; -3,02</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-16,25%</t>
+          <t>-22,15%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,06%</t>
+          <t>-18,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-23,82%</t>
+          <t>-18,91%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 10,9</t>
+          <t>-13,78; 9,98</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-25,87; -4,32</t>
+          <t>-26,39; -5,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,43; -4,84</t>
+          <t>-32,48; -10,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 14,98</t>
+          <t>-25,83; 13,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 28,5</t>
+          <t>-13,31; 31,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-50,48; -14,87</t>
+          <t>-33,79; 1,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 8,32</t>
+          <t>-14,85; 8,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 10,49</t>
+          <t>-14,73; 7,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,78; -13,02</t>
+          <t>-29,01; -8,72</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,64</t>
+          <t>-8,9</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>-1,71</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 12,79</t>
+          <t>-4,03; 12,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,09; 16,25</t>
+          <t>-0,64; 15,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 7,2</t>
+          <t>-19,59; 3,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,44</t>
+          <t>2,02; 8,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,6; 10,05</t>
+          <t>3,37; 10,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,55</t>
+          <t>-3,82; 2,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,9</t>
+          <t>1,58; 8,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,12; 10,64</t>
+          <t>3,91; 10,71</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 4,54</t>
+          <t>-5,14; 1,91</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-12,52%</t>
+          <t>-19,74%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>-4,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>-7,96%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 31,18</t>
+          <t>-8,26; 31,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,1; 39,67</t>
+          <t>-1,52; 38,81</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-37,39; 16,53</t>
+          <t>-41,16; 7,88</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11,21; 59,27</t>
+          <t>11,17; 58,22</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>21,19; 70,33</t>
+          <t>19,75; 72,01</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 23,58</t>
+          <t>-22,79; 17,33</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,33; 39,75</t>
+          <t>6,83; 40,15</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>18,35; 52,8</t>
+          <t>17,32; 53,14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 22,37</t>
+          <t>-22,87; 9,58</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-9,1</t>
+          <t>-7,05</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,68</t>
+          <t>-3,7</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,72</t>
+          <t>-1,03; 3,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,75</t>
+          <t>-0,42; 4,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-20,58; -4,69</t>
+          <t>-9,54; -4,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,28</t>
+          <t>-0,85; 3,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,36</t>
+          <t>4,0; 8,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 18,54</t>
+          <t>-2,29; 1,55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,87</t>
+          <t>-0,68; 2,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,88</t>
+          <t>2,37; 5,91</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 2,81</t>
+          <t>-5,51; -2,13</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-16,56%</t>
+          <t>-12,84%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>-1,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-6,8%</t>
+          <t>-9,38%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 6,93</t>
+          <t>-1,98; 7,03</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 8,81</t>
+          <t>-0,71; 8,55</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,59; -8,53</t>
+          <t>-17,03; -8,31</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 14,09</t>
+          <t>-3,47; 14,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,76; 35,18</t>
+          <t>15,42; 35,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 76,47</t>
+          <t>-8,91; 6,7</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 7,42</t>
+          <t>-1,68; 6,93</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5,62; 15,27</t>
+          <t>5,75; 15,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 7,31</t>
+          <t>-13,74; -5,51</t>
         </is>
       </c>
     </row>
